--- a/De-Para_Empresa_0003.xlsx
+++ b/De-Para_Empresa_0003.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.1.01.01.0001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>067</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.1.01.02.0001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -470,12 +470,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>086</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.1.01.02.0002</t>
+          <t>4120300003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -487,12 +487,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>020</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.1.01.02.0003</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -504,12 +504,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>032</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.1.01.01.0011</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -521,12 +521,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>036</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.1.01.01.0011</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -538,12 +538,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.1.01.01.0005</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -555,12 +555,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>066</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.1.01.01.0005</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -572,12 +572,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.1.01.02.0003</t>
+          <t>4120300010</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -589,233 +589,233 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>068</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.1.01.02.0001</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.1.02.02.0005</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.1.05.01.0001</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>084</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.1.02.02.0005</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.1.01.02.0002</t>
+          <t>2140100002</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>086</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300009</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.1.02.02.0005</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.1.02.02.0005</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.1.02.02.0005</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.1.05.02.0001</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.1.05.02.0002</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300009</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.1.05.03.0002</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300009</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.1.02.02.0002</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2140100001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.1.02.02.0003</t>
+          <t>2140100001</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.1.05.01.0001</t>
+          <t>4120300001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -827,335 +827,1804 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GPS_PATRONAL</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4120300012</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GPS_RAT</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4120300009</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GPS_TERCEIROS</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4120300010</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FGTS</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>002</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>013</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>014</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>020</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>025</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>055</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>066</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4120300006</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>068</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4120300005</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>069</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>071</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>082</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4120300003</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4120300010</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4120300008</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4120300012</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4120300010</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1140100004</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4120300009</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4120300009</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4120300008</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4120300012</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4120300010</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2140100013</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>4120300009</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>4120300009</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2140100013</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>4120300009</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4120300012</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>4120300008</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4120300008</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1140800007</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1140100008</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2140100002</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2140100013</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2140100007</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2140100007</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2140100010</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>013</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2140100010</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2140100008</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>014</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>4120300005</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>057</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4120300008</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>094</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>4120300012</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2140200004</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2140200004</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1140100002</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>4120300010</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>4120300008</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>4120300012</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>4120300008</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1140100002</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4120300001</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>4120300005</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2140100007</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2140100012</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2140100007</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sócios :</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>4120300005</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2140200004</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2140100011</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2140100011</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>4120300005</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2140100011</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2140200002</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2140100011</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2140100007</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Empresa Funcionários:</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2140100011</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2140100002</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2140100013</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2140100013</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>GPS_PATRONAL</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4120300005</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>GPS_RAT</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>4120300005</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>GPS_TERCEIROS</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>4120300005</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2140100005</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>FGTS</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>4120300006</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2140100002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
